--- a/data/trans_bre/IP1003-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP1003-Edad-trans_bre.xlsx
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 1,86</t>
+          <t>-4,26; 1,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 0,56</t>
+          <t>-3,31; 0,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 2,34</t>
+          <t>-2,06; 2,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 1,1</t>
+          <t>-4,79; 1,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 272,08</t>
+          <t>-91,15; 269,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 4,45</t>
+          <t>-2,78; 3,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 1,28</t>
+          <t>-5,05; 1,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 1,54</t>
+          <t>-4,57; 1,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 2,07</t>
+          <t>-5,57; 2,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,18; 106,05</t>
+          <t>-37,83; 98,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-68,62; 35,34</t>
+          <t>-65,45; 39,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-71,32; 70,8</t>
+          <t>-72,88; 60,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-80,82; 83,81</t>
+          <t>-76,31; 88,14</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 5,64</t>
+          <t>-6,15; 5,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 2,05</t>
+          <t>-7,87; 2,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 5,75</t>
+          <t>-4,42; 4,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 2,01</t>
+          <t>-7,5; 2,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-45,82; 92,05</t>
+          <t>-50,94; 93,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-66,04; 40,82</t>
+          <t>-67,32; 36,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-41,94; 131,62</t>
+          <t>-48,33; 106,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-66,59; 36,18</t>
+          <t>-63,92; 46,27</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 0,85</t>
+          <t>-7,32; 1,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 4,88</t>
+          <t>-3,99; 5,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 2,55</t>
+          <t>-5,91; 3,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 0,25</t>
+          <t>-9,25; 0,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-65,39; 14,63</t>
+          <t>-65,46; 14,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-44,09; 95,96</t>
+          <t>-44,72; 109,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-59,96; 55,09</t>
+          <t>-63,12; 65,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-63,64; 5,02</t>
+          <t>-64,7; 1,77</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 1,07</t>
+          <t>-2,94; 1,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 0,58</t>
+          <t>-3,35; 0,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,31</t>
+          <t>-2,5; 1,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,38; -0,28</t>
+          <t>-5,23; -0,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-38,7; 18,26</t>
+          <t>-36,68; 19,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-46,85; 13,7</t>
+          <t>-47,5; 12,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-42,83; 31,24</t>
+          <t>-40,26; 27,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-53,72; -3,9</t>
+          <t>-54,49; -4,34</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1003-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP1003-Edad-trans_bre.xlsx
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 1,97</t>
+          <t>-5,25; 1,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 0,61</t>
+          <t>-2,96; 0,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 2,48</t>
+          <t>-2,09; 2,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 1,09</t>
+          <t>-3,34; 1,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-91,15; 269,62</t>
+          <t>-100,0; 181,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 3,93</t>
+          <t>-2,67; 4,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 1,42</t>
+          <t>-5,05; 1,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 1,91</t>
+          <t>-4,22; 1,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 2,12</t>
+          <t>-5,62; 1,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-37,83; 98,13</t>
+          <t>-37,97; 111,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-65,45; 39,35</t>
+          <t>-66,77; 41,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-72,88; 60,89</t>
+          <t>-69,18; 59,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-76,31; 88,14</t>
+          <t>-74,56; 71,35</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 5,34</t>
+          <t>-5,9; 5,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 2,07</t>
+          <t>-8,39; 1,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 4,66</t>
+          <t>-3,87; 5,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 2,5</t>
+          <t>-7,83; 1,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-50,94; 93,77</t>
+          <t>-51,21; 83,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-67,32; 36,46</t>
+          <t>-67,12; 31,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-48,33; 106,02</t>
+          <t>-42,91; 127,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-63,92; 46,27</t>
+          <t>-67,13; 34,96</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 1,03</t>
+          <t>-7,42; 0,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 5,29</t>
+          <t>-4,38; 4,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 3,06</t>
+          <t>-6,16; 2,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 0,14</t>
+          <t>-8,72; 0,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-65,46; 14,81</t>
+          <t>-64,87; 14,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-44,72; 109,13</t>
+          <t>-46,51; 97,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-63,12; 65,13</t>
+          <t>-64,01; 55,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,7; 1,77</t>
+          <t>-61,03; 7,93</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 1,11</t>
+          <t>-3,01; 1,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 0,62</t>
+          <t>-3,45; 0,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 1,2</t>
+          <t>-2,52; 1,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,23; -0,31</t>
+          <t>-5,46; -0,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-36,68; 19,83</t>
+          <t>-37,86; 23,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-47,5; 12,77</t>
+          <t>-46,73; 9,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-40,26; 27,79</t>
+          <t>-40,02; 34,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-54,49; -4,34</t>
+          <t>-54,75; -2,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1003-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP1003-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,42</t>
+          <t>-0,49</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-43,23%</t>
+          <t>-50,08%</t>
         </is>
       </c>
     </row>
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 1,66</t>
+          <t>-4,77; 1,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 0,58</t>
+          <t>-3,38; 0,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 2,51</t>
+          <t>-1,77; 2,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 1,11</t>
+          <t>-4,04; 0,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 181,58</t>
+          <t>-100,0; 272,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,67</t>
+          <t>-0,39</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-32,65%</t>
+          <t>-9,16%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 4,54</t>
+          <t>-2,88; 4,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 1,48</t>
+          <t>-5,17; 1,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 1,53</t>
+          <t>-4,59; 1,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 1,89</t>
+          <t>-4,05; 3,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-37,97; 111,2</t>
+          <t>-39,18; 106,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-66,77; 41,55</t>
+          <t>-68,62; 35,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-69,18; 59,71</t>
+          <t>-71,32; 70,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-74,56; 71,35</t>
+          <t>-72,73; 144,77</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,55</t>
+          <t>-1,91</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-29,67%</t>
+          <t>-23,09%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 5,07</t>
+          <t>-5,35; 5,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 1,85</t>
+          <t>-7,96; 2,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 5,33</t>
+          <t>-3,79; 5,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 1,79</t>
+          <t>-6,99; 2,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-51,21; 83,04</t>
+          <t>-45,82; 92,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-67,12; 31,53</t>
+          <t>-66,04; 40,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-42,91; 127,92</t>
+          <t>-41,94; 131,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-67,13; 34,96</t>
+          <t>-62,27; 47,79</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,92</t>
+          <t>-3,65</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-34,65%</t>
+          <t>-30,68%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 0,78</t>
+          <t>-7,74; 0,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 4,99</t>
+          <t>-4,09; 4,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 2,36</t>
+          <t>-5,93; 2,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 0,62</t>
+          <t>-8,8; 0,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-64,87; 14,72</t>
+          <t>-65,39; 14,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,51; 97,68</t>
+          <t>-44,09; 95,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-64,01; 55,62</t>
+          <t>-59,96; 55,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-61,03; 7,93</t>
+          <t>-59,07; 8,75</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-2,73</t>
+          <t>-2,29</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-33,09%</t>
+          <t>-27,34%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 1,37</t>
+          <t>-2,97; 1,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 0,43</t>
+          <t>-3,49; 0,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 1,37</t>
+          <t>-2,58; 1,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,46; -0,2</t>
+          <t>-4,96; 0,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-37,86; 23,97</t>
+          <t>-38,7; 18,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-46,73; 9,24</t>
+          <t>-46,85; 13,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-40,02; 34,68</t>
+          <t>-42,83; 31,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-54,75; -2,51</t>
+          <t>-50,05; 3,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1003-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP1003-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,187 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-1,22</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,92</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,31</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,49</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-41,25%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-64,78%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>29,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-50,08%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-1.218996499258137</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.9228511603030558</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.3101335132313157</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-0.490127755291826</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.4124581784594297</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.647790855830167</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.2957893053293175</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.5007518951353988</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-4,77; 1,86</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-3,38; 0,56</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-1,77; 2,34</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-4,04; 0,97</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 272,08</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-4.772088658695941</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-3.376055697132173</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-1.766781222499683</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-4.035711453754138</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1.859619569770286</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.5614682164787748</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>2.336112586711379</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0.9674117873849836</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>2.720784340499423</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,6</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-1,83</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-1,39</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,39</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>10,15%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-30,75%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-29,48%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-9,16%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-2,88; 4,45</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-5,17; 1,28</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-4,59; 1,54</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-4,05; 3,61</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-39,18; 106,05</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-68,62; 35,34</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-71,32; 70,8</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-72,73; 144,77</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.5980556442206644</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-1.831543084766559</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-1.392087123947448</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.388935692633989</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.1015155774755294</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.3075341289218915</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.2948214965072327</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.09155521331072604</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,21</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-2,92</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,62</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,91</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-2,33%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-31,43%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,37%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-23,09%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.876231890576844</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-5.173985031568065</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-4.589231891079213</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-4.048437097576554</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.3918492790894708</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.6861804369166982</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.7132176314808942</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.7272954922042386</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-5,35; 5,64</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-7,96; 2,05</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-3,79; 5,75</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-6,99; 2,51</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-45,82; 92,05</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-66,04; 40,82</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-41,94; 131,62</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-62,27; 47,79</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>4.445102323692844</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.281410921901163</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.53653380268045</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>3.610935885267394</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.060536557538926</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.3534014118147239</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.7079909828338508</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>1.447668992421858</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +807,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-3,33</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,27</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-1,69</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-3,65</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-36,25%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,71%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-23,3%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-30,68%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.2052682738845873</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-2.921925138984745</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.622289434338956</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-1.909421734090394</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.02328444695187044</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.3143352937914181</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.09371906803865673</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.2309225304953795</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-7,74; 0,85</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-4,09; 4,88</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-5,93; 2,55</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-8,8; 0,66</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-65,39; 14,63</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-44,09; 95,96</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-59,96; 55,09</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-59,07; 8,75</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-5.348839728664522</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-7.958957096571413</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-3.785634455298056</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-6.994689898889973</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.4582286759308296</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.6604089919984001</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.4193990692032252</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.622713549093818</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>5.63565780730694</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2.054890323319719</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5.74541500463752</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>2.510325892642158</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.9205325645095755</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.4081568219030648</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.316238034161663</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.4778635495264937</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-3.334872030645473</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.2699603380221266</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-1.686008710863796</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-3.653146290915016</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.3625280152589098</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.03706322255364181</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.233045546127062</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.3067762422289421</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-7.736892018732775</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-4.089356211646301</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-5.9305745430789</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-8.79588349213342</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.6539279566329027</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.4409310818554746</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.5996188128508655</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.5906675677341529</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.8531063483740423</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>4.881869552886934</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.553876963940967</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.6624798761386784</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.1462806380736838</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.9596127990082753</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.5508529810479577</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.087478040653806</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,95</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-1,41</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,62</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-2,29</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-13,69%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-23,02%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-11,97%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-27,34%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,97; 1,07</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3,49; 0,58</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,58; 1,31</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-4,96; 0,21</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-38,7; 18,26</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-46,85; 13,7</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-42,83; 31,24</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-50,05; 3,28</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.9464748344904045</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-1.405239041899653</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.6204013575452534</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-2.286393119065867</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.1368949393426817</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.230207948989328</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.1197161939461218</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.2734041732391645</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.97284247903847</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.494179811215464</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-2.576880149412136</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-4.957075127453722</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.3869689790917459</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.4684907827264612</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.4282743232494939</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.5005083076296172</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.071252964359931</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.5767018124861668</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.308614819353522</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.2107498514385048</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.1825511213538469</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.1370033663594252</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.3124156392450821</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.03278702370073539</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1105,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
